--- a/data/BladderCancer_Ex_Val_clini_trial.xlsx
+++ b/data/BladderCancer_Ex_Val_clini_trial.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/4476224/Desktop/RejniakLab_projects/Projects/2026_PETIL_proj/PETIL_70_30_spl/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C995EE49-F4AB-434E-9D3C-5E91D2B0BE97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ABFA350-23ED-514E-A2BA-49DB2A0877D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="17680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="93">
   <si>
     <t>ID</t>
   </si>
@@ -310,9 +310,6 @@
   </si>
   <si>
     <t>BLT-017</t>
-  </si>
-  <si>
-    <t>Zemp</t>
   </si>
   <si>
     <t>B132</t>
@@ -1790,266 +1787,253 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" style="9" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="9" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="9" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" style="8" customWidth="1"/>
-    <col min="6" max="6" width="15" style="8" customWidth="1"/>
-    <col min="7" max="7" width="9.33203125" style="9" customWidth="1"/>
-    <col min="8" max="8" width="10" style="9" customWidth="1"/>
-    <col min="9" max="9" width="9" style="9" customWidth="1"/>
-    <col min="10" max="10" width="10.1640625" style="9" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" style="9" customWidth="1"/>
-    <col min="12" max="12" width="9.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.5" style="9" customWidth="1"/>
-    <col min="14" max="14" width="14.83203125" style="9" customWidth="1"/>
-    <col min="15" max="15" width="17.33203125" style="9" customWidth="1"/>
-    <col min="16" max="16" width="23.83203125" style="9" customWidth="1"/>
-    <col min="17" max="17" width="21.5" style="9" customWidth="1"/>
-    <col min="18" max="18" width="23.83203125" style="9" customWidth="1"/>
-    <col min="19" max="19" width="18.1640625" style="9" customWidth="1"/>
-    <col min="20" max="16384" width="8.83203125" style="9"/>
+    <col min="2" max="2" width="12.6640625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="9" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="15" style="8" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" style="9" customWidth="1"/>
+    <col min="7" max="7" width="10" style="9" customWidth="1"/>
+    <col min="8" max="8" width="9" style="9" customWidth="1"/>
+    <col min="9" max="9" width="10.1640625" style="9" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" style="9" customWidth="1"/>
+    <col min="11" max="11" width="9.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5" style="9" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" style="9" customWidth="1"/>
+    <col min="14" max="14" width="17.33203125" style="9" customWidth="1"/>
+    <col min="15" max="15" width="23.83203125" style="9" customWidth="1"/>
+    <col min="16" max="16" width="21.5" style="9" customWidth="1"/>
+    <col min="17" max="17" width="23.83203125" style="9" customWidth="1"/>
+    <col min="18" max="18" width="18.1640625" style="9" customWidth="1"/>
+    <col min="19" max="16384" width="8.83203125" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="12" customFormat="1" ht="81" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" s="12" customFormat="1" ht="81" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="5">
+        <v>72</v>
+      </c>
+      <c r="C2" s="5">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5">
         <v>2</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B2" s="5">
-        <v>4</v>
-      </c>
-      <c r="C2" s="5">
-        <v>72</v>
-      </c>
-      <c r="D2" s="5">
-        <v>1</v>
-      </c>
       <c r="E2" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>0</v>
+        <v>27.87</v>
       </c>
       <c r="G2" s="5">
-        <v>27.87</v>
+        <v>0</v>
       </c>
       <c r="H2" s="5">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5">
         <v>3</v>
       </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5">
+      <c r="I2" s="5"/>
+      <c r="J2" s="5">
         <v>3</v>
       </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5">
-        <v>1</v>
-      </c>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5">
+        <v>1</v>
+      </c>
+      <c r="M2" s="5"/>
       <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5">
+      <c r="O2" s="5">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="Q2" s="6">
-        <v>0</v>
-      </c>
-      <c r="R2" s="5">
+      <c r="P2" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5">
         <v>5</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="R2" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B3" s="5">
+        <v>71</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>31.25</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
         <v>4</v>
       </c>
-      <c r="C3" s="5">
-        <v>71</v>
-      </c>
-      <c r="D3" s="5">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5">
-        <v>1</v>
-      </c>
-      <c r="F3" s="5">
-        <v>1</v>
-      </c>
-      <c r="G3" s="5">
-        <v>31.25</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
       <c r="I3" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3" s="5">
         <v>5</v>
       </c>
       <c r="K3" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>1</v>
       </c>
-      <c r="N3" s="5">
-        <v>1</v>
-      </c>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5">
+      <c r="N3" s="5"/>
+      <c r="O3" s="5">
         <v>32</v>
       </c>
-      <c r="Q3" s="6">
+      <c r="P3" s="6">
         <v>333000000</v>
       </c>
-      <c r="R3" s="5">
+      <c r="Q3" s="5">
         <v>12</v>
       </c>
-      <c r="S3" s="5" t="s">
+      <c r="R3" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>80</v>
       </c>
       <c r="B4" s="5">
+        <v>71</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5">
+        <v>31.22</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
         <v>4</v>
       </c>
-      <c r="C4" s="5">
-        <v>71</v>
-      </c>
-      <c r="D4" s="5">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5">
-        <v>1</v>
-      </c>
-      <c r="F4" s="5">
-        <v>1</v>
-      </c>
-      <c r="G4" s="5">
-        <v>31.22</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
       <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5">
         <v>4</v>
       </c>
-      <c r="J4" s="5">
-        <v>2</v>
-      </c>
       <c r="K4" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>1</v>
       </c>
       <c r="N4" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O4" s="5">
-        <v>8</v>
-      </c>
-      <c r="P4" s="5">
         <v>0.16400000000000001</v>
       </c>
-      <c r="Q4" s="6">
-        <v>0</v>
-      </c>
-      <c r="R4" s="5">
+      <c r="P4" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="5">
         <v>6</v>
       </c>
-      <c r="S4" s="5" t="s">
+      <c r="R4" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B5" s="5">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="C5" s="5">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
@@ -2058,597 +2042,560 @@
         <v>1</v>
       </c>
       <c r="F5" s="5">
-        <v>1</v>
+        <v>23.59</v>
       </c>
       <c r="G5" s="5">
-        <v>23.59</v>
+        <v>0</v>
       </c>
       <c r="H5" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
         <v>3</v>
       </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
       <c r="K5" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>1</v>
       </c>
-      <c r="N5" s="5">
-        <v>1</v>
-      </c>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5">
+      <c r="N5" s="5"/>
+      <c r="O5" s="5">
         <v>0.26</v>
       </c>
-      <c r="Q5" s="6">
+      <c r="P5" s="6">
         <v>3900000</v>
       </c>
-      <c r="R5" s="5">
+      <c r="Q5" s="5">
         <v>6</v>
       </c>
-      <c r="S5" s="5" t="s">
+      <c r="R5" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>82</v>
       </c>
       <c r="B6" s="5">
+        <v>61</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5">
+        <v>25</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5">
         <v>4</v>
       </c>
-      <c r="C6" s="5">
-        <v>61</v>
-      </c>
-      <c r="D6" s="5">
-        <v>1</v>
-      </c>
-      <c r="E6" s="5">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5">
-        <v>1</v>
-      </c>
-      <c r="G6" s="5">
-        <v>25</v>
-      </c>
-      <c r="H6" s="5">
-        <v>1</v>
-      </c>
       <c r="I6" s="5">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J6" s="5">
         <v>11</v>
       </c>
       <c r="K6" s="5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="5">
         <v>1</v>
       </c>
       <c r="N6" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O6" s="5">
+        <v>0.35099999999999998</v>
+      </c>
+      <c r="P6" s="6">
+        <v>1760000</v>
+      </c>
+      <c r="Q6" s="5">
         <v>8</v>
       </c>
-      <c r="P6" s="5">
-        <v>0.35099999999999998</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>1760000</v>
-      </c>
-      <c r="R6" s="5">
-        <v>8</v>
-      </c>
-      <c r="S6" s="5" t="s">
+      <c r="R6" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B7" s="5">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="C7" s="5">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="D7" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="5">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5">
         <v>26.82</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5">
-        <v>1</v>
-      </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5">
-        <v>1</v>
-      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5">
+        <v>1</v>
+      </c>
+      <c r="K7" s="5"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5">
+      <c r="O7" s="5">
         <v>0.6</v>
       </c>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="5">
+      <c r="P7" s="6"/>
+      <c r="Q7" s="5">
         <v>7</v>
       </c>
-      <c r="S7" s="5" t="s">
+      <c r="R7" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>84</v>
       </c>
       <c r="B8" s="5">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="C8" s="5">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="D8" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5">
         <v>2</v>
       </c>
       <c r="F8" s="5">
-        <v>2</v>
-      </c>
-      <c r="G8" s="5">
         <v>23.81</v>
       </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5">
+      <c r="G8" s="5"/>
+      <c r="H8" s="5">
         <v>3</v>
       </c>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5">
+      <c r="I8" s="5"/>
+      <c r="J8" s="5">
         <v>3</v>
       </c>
+      <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5">
+      <c r="O8" s="5">
         <v>0.1</v>
       </c>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="5">
+      <c r="P8" s="6"/>
+      <c r="Q8" s="5">
         <v>15</v>
       </c>
-      <c r="S8" s="5" t="s">
+      <c r="R8" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B9" s="5">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="C9" s="5">
-        <v>59</v>
-      </c>
-      <c r="D9" s="5">
-        <v>1</v>
-      </c>
-      <c r="E9" s="11">
+        <v>1</v>
+      </c>
+      <c r="D9" s="11">
         <v>2</v>
       </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
       <c r="F9" s="5">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5">
         <v>47.19</v>
       </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5">
-        <v>1</v>
-      </c>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5">
-        <v>1</v>
-      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5">
+        <v>1</v>
+      </c>
+      <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5">
+      <c r="O9" s="5">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="5">
+      <c r="P9" s="6"/>
+      <c r="Q9" s="5">
         <v>48</v>
       </c>
-      <c r="S9" s="5" t="s">
+      <c r="R9" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>86</v>
       </c>
       <c r="B10" s="5">
+        <v>76</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
         <v>2</v>
       </c>
-      <c r="C10" s="5">
-        <v>76</v>
-      </c>
-      <c r="D10" s="5">
-        <v>1</v>
-      </c>
       <c r="E10" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" s="5">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5">
         <v>29.84</v>
       </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5">
-        <v>1</v>
-      </c>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5">
-        <v>1</v>
-      </c>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5">
+        <v>1</v>
+      </c>
+      <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5">
+      <c r="O10" s="5">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="5">
+      <c r="P10" s="6"/>
+      <c r="Q10" s="5">
         <v>7</v>
       </c>
-      <c r="S10" s="5" t="s">
+      <c r="R10" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>87</v>
       </c>
       <c r="B11" s="5">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="C11" s="5">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="D11" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="5">
-        <v>1</v>
-      </c>
-      <c r="G11" s="5">
         <v>27.3</v>
       </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="11">
+      <c r="G11" s="5"/>
+      <c r="H11" s="11">
         <v>3</v>
       </c>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5">
+      <c r="I11" s="5"/>
+      <c r="J11" s="5">
         <v>3</v>
       </c>
+      <c r="K11" s="5"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5">
+      <c r="O11" s="5">
         <v>1.4</v>
       </c>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="5">
+      <c r="P11" s="6"/>
+      <c r="Q11" s="5">
         <v>35</v>
       </c>
-      <c r="S11" s="5" t="s">
+      <c r="R11" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>88</v>
       </c>
       <c r="B12" s="5">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="C12" s="5">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="D12" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="5">
-        <v>1</v>
-      </c>
-      <c r="G12" s="5">
         <v>26.45</v>
       </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="11">
+      <c r="G12" s="5"/>
+      <c r="H12" s="11">
         <v>3</v>
       </c>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5">
+      <c r="I12" s="5"/>
+      <c r="J12" s="5">
         <v>3</v>
       </c>
+      <c r="K12" s="5"/>
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5">
+      <c r="O12" s="5">
         <v>0.5</v>
       </c>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="5">
+      <c r="P12" s="6"/>
+      <c r="Q12" s="5">
         <v>28</v>
       </c>
-      <c r="S12" s="5" t="s">
+      <c r="R12" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>92</v>
+      <c r="B13" s="5">
+        <v>84</v>
       </c>
       <c r="C13" s="5">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="D13" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" s="5">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5">
         <v>25.54</v>
       </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="11">
-        <v>1</v>
-      </c>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5">
-        <v>1</v>
-      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="11">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5">
+        <v>1</v>
+      </c>
+      <c r="K13" s="5"/>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5">
+      <c r="O13" s="5">
         <v>0.2</v>
       </c>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="5">
+      <c r="P13" s="6"/>
+      <c r="Q13" s="5">
         <v>14</v>
       </c>
-      <c r="S13" s="5" t="s">
+      <c r="R13" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>92</v>
+      <c r="B14" s="5">
+        <v>69</v>
       </c>
       <c r="C14" s="5">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="D14" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="5">
+        <v>1</v>
+      </c>
+      <c r="F14" s="5">
+        <v>28.12</v>
+      </c>
+      <c r="G14" s="5"/>
+      <c r="H14" s="11">
         <v>2</v>
       </c>
-      <c r="F14" s="5">
-        <v>1</v>
-      </c>
-      <c r="G14" s="5">
-        <v>28.12</v>
-      </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="11">
+      <c r="I14" s="5"/>
+      <c r="J14" s="5">
         <v>2</v>
       </c>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5">
-        <v>2</v>
-      </c>
+      <c r="K14" s="5"/>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5">
+      <c r="O14" s="5">
         <v>0.1</v>
       </c>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="5">
+      <c r="P14" s="6"/>
+      <c r="Q14" s="5">
         <v>6</v>
       </c>
-      <c r="S14" s="5" t="s">
+      <c r="R14" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>90</v>
       </c>
       <c r="B15" s="5">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="C15" s="5">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="D15" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="5">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5">
         <v>27.95</v>
       </c>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5">
-        <v>1</v>
-      </c>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5">
-        <v>1</v>
-      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5">
+        <v>1</v>
+      </c>
+      <c r="K15" s="5"/>
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5">
+      <c r="O15" s="5">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="5">
+      <c r="P15" s="6"/>
+      <c r="Q15" s="5">
         <v>13</v>
       </c>
-      <c r="S15" s="5" t="s">
+      <c r="R15" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="7"/>
       <c r="B16" s="7">
-        <f>COUNTA(B2:B15)</f>
+        <f t="shared" ref="B16:R16" si="0">COUNTA(B2:B15)</f>
         <v>14</v>
       </c>
       <c r="C16" s="7">
-        <f>COUNTA(C2:C15)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="D16" s="7">
-        <f>COUNTA(D2:D15)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="E16" s="7">
-        <f>COUNTA(E2:E15)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="F16" s="7">
-        <f>COUNTA(F2:F15)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="G16" s="7">
-        <f>COUNTA(G2:G15)</f>
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="H16" s="7">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="H16" s="7">
-        <f>COUNTA(H2:H15)</f>
+      <c r="I16" s="7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="J16" s="7">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="K16" s="7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="L16" s="7">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I16" s="7">
-        <f>COUNTA(I2:I15)</f>
+      <c r="M16" s="7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="N16" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O16" s="7">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="J16" s="7">
-        <f>COUNTA(J2:J15)</f>
-        <v>4</v>
-      </c>
-      <c r="K16" s="7">
-        <f>COUNTA(K2:K15)</f>
+      <c r="P16" s="7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="Q16" s="7">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="L16" s="7">
-        <f>COUNTA(L2:L15)</f>
-        <v>4</v>
-      </c>
-      <c r="M16" s="7">
-        <f>COUNTA(M2:M15)</f>
-        <v>5</v>
-      </c>
-      <c r="N16" s="7">
-        <f>COUNTA(N2:N15)</f>
-        <v>4</v>
-      </c>
-      <c r="O16" s="7">
-        <f>COUNTA(O2:O15)</f>
-        <v>2</v>
-      </c>
-      <c r="P16" s="7">
-        <f>COUNTA(P2:P15)</f>
-        <v>14</v>
-      </c>
-      <c r="Q16" s="7">
-        <f>COUNTA(Q2:Q15)</f>
-        <v>5</v>
-      </c>
       <c r="R16" s="7">
-        <f>COUNTA(R2:R15)</f>
-        <v>14</v>
-      </c>
-      <c r="S16" s="7">
-        <f>COUNTA(S2:S15)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
   </sheetData>
   <dataValidations xWindow="938" yWindow="226" count="10">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="0 - benign    6 - micropapillary_x000a_1 - TCC/UC  7 -  sarcomatoid_x000a_2 - SCC        8 - small cell_x000a_3 - Adenocarcinoma   9 - UC w/ neuroendocrine features_x000a_4 - UC w/ squamous diff  10 - Plamacytoid  _x000a_5 - UC w/ glandular diff    11- mixed" sqref="N1" xr:uid="{00000000-0002-0000-0000-000014000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="0 - benign_x000a_1 - TCC/UC (transitional cell/urothelial)_x000a_2 - SCC (squamous cell)_x000a_3 - Adenocarcinoma_x000a_4 - UC w/ squamous diff_x000a_5 - UC w/ glandular diff_x000a_6 - micropapillary_x000a_7  -sarcomatoid_x000a_8 - small cell_x000a_9 -UC w/ neuroendocrine features_x000a_10 -Plamacytoid  _x000a_11-mixed" sqref="M1" xr:uid="{00000000-0002-0000-0000-000019000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="0-T0 7-T3_x000a_1-Ta 8-T3a_x000a_2-Tis 9-T3b_x000a_3-T1 10-T4_x000a_4-T2 11-T4a_x000a_5-T2a 12-T4b_x000a_6-T2b 13-Tx_x000a_" sqref="K1 I1" xr:uid="{00000000-0002-0000-0000-00001C000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="0 - Unknown/Other_x000a_1 - White_x000a_2 - Black_x000a_3 - Asian_x000a_4 - Naïve Hawaiian/Pacific Islander_x000a_5 - American Indian/Alaskan Native" sqref="D1" xr:uid="{00000000-0002-0000-0000-000021000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="0 - none    _x000a_1 - squamous   _x000a_2 - adenocarcinoma  _x000a_3 - sarcomatoid _x000a_4 - small cell_x000a_5 - neuroendocrine_x000a_6 - micropapillary_x000a_7 - plasmacytoid_x000a_8 - prostatic adenocarcinoma" sqref="O1:O1048576" xr:uid="{00000000-0002-0000-0000-000013000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="0 = N0_x000a_1 = N1_x000a_2 = N2_x000a_3 = N3_x000a_4 = Nx" sqref="L1:L1048576" xr:uid="{00000000-0002-0000-0000-000015000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="0 = T0     8 = T3a_x000a_1 = Ta      9 = T3b_x000a_2 = Tis      10 = T4_x000a_3 = T1      11 = T4a_x000a_4 = T2      12 = T4b_x000a_5 = T2a     13 = TX_x000a_6 = T2b     _x000a_7 = T3" sqref="J1:J1048576" xr:uid="{00000000-0002-0000-0000-000016000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="0 = no NAC_x000a_1 = NAC" sqref="H1:H1048576" xr:uid="{00000000-0002-0000-0000-000018000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1 = Radical Cystectomy_x000a_2 = TURBT" sqref="E1:E1048576" xr:uid="{CD3F280F-85D1-254C-8AE5-90AE82D0BCEE}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="0 - Never Smoked_x000a_1 - Ever Smoked_x000a_2 - Current Smoker" sqref="F1:F1048576" xr:uid="{474D1087-1F4A-BA41-932B-9F2F0228F032}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="0 - benign    6 - micropapillary_x000a_1 - TCC/UC  7 -  sarcomatoid_x000a_2 - SCC        8 - small cell_x000a_3 - Adenocarcinoma   9 - UC w/ neuroendocrine features_x000a_4 - UC w/ squamous diff  10 - Plamacytoid  _x000a_5 - UC w/ glandular diff    11- mixed" sqref="M1" xr:uid="{00000000-0002-0000-0000-000014000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="0 - benign_x000a_1 - TCC/UC (transitional cell/urothelial)_x000a_2 - SCC (squamous cell)_x000a_3 - Adenocarcinoma_x000a_4 - UC w/ squamous diff_x000a_5 - UC w/ glandular diff_x000a_6 - micropapillary_x000a_7  -sarcomatoid_x000a_8 - small cell_x000a_9 -UC w/ neuroendocrine features_x000a_10 -Plamacytoid  _x000a_11-mixed" sqref="L1" xr:uid="{00000000-0002-0000-0000-000019000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="0-T0 7-T3_x000a_1-Ta 8-T3a_x000a_2-Tis 9-T3b_x000a_3-T1 10-T4_x000a_4-T2 11-T4a_x000a_5-T2a 12-T4b_x000a_6-T2b 13-Tx_x000a_" sqref="J1 H1" xr:uid="{00000000-0002-0000-0000-00001C000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="0 - Unknown/Other_x000a_1 - White_x000a_2 - Black_x000a_3 - Asian_x000a_4 - Naïve Hawaiian/Pacific Islander_x000a_5 - American Indian/Alaskan Native" sqref="C1" xr:uid="{00000000-0002-0000-0000-000021000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="0 - none    _x000a_1 - squamous   _x000a_2 - adenocarcinoma  _x000a_3 - sarcomatoid _x000a_4 - small cell_x000a_5 - neuroendocrine_x000a_6 - micropapillary_x000a_7 - plasmacytoid_x000a_8 - prostatic adenocarcinoma" sqref="N1:N1048576" xr:uid="{00000000-0002-0000-0000-000013000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="0 = N0_x000a_1 = N1_x000a_2 = N2_x000a_3 = N3_x000a_4 = Nx" sqref="K1:K1048576" xr:uid="{00000000-0002-0000-0000-000015000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="0 = T0     8 = T3a_x000a_1 = Ta      9 = T3b_x000a_2 = Tis      10 = T4_x000a_3 = T1      11 = T4a_x000a_4 = T2      12 = T4b_x000a_5 = T2a     13 = TX_x000a_6 = T2b     _x000a_7 = T3" sqref="I1:I1048576" xr:uid="{00000000-0002-0000-0000-000016000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="0 = no NAC_x000a_1 = NAC" sqref="G1:G1048576" xr:uid="{00000000-0002-0000-0000-000018000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="1 = Radical Cystectomy_x000a_2 = TURBT" sqref="D1:D1048576" xr:uid="{CD3F280F-85D1-254C-8AE5-90AE82D0BCEE}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="0 - Never Smoked_x000a_1 - Ever Smoked_x000a_2 - Current Smoker" sqref="E1:E1048576" xr:uid="{474D1087-1F4A-BA41-932B-9F2F0228F032}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
